--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M32B3_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M32B3_IN_Piura.xlsx
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>6.12</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="C12" s="29">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>45.86</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>45.74</v>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>2.28</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1918,11 +1918,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>50.9723</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1943,11 +1943,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>3.1211</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>6.12</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1968,11 +1968,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>47.8512</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>93.88</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2166,11 +2166,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>50.9956</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2289,6 +2289,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2398,6 +2399,7 @@
       <c r="F12" s="17" t="inlineStr"/>
       <c r="G12" s="17" t="inlineStr"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
@@ -2442,6 +2444,7 @@
       <c r="G15" s="8" t="n"/>
       <c r="H15" s="8" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17" ht="228" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
@@ -2661,11 +2664,11 @@
       </c>
       <c r="B12" s="32">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>62.44</v>
       </c>
       <c r="C12" s="23">
         <f>SUM(C10:C11)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
@@ -2675,19 +2678,19 @@
       <c r="E12" s="17" t="inlineStr"/>
       <c r="F12" s="17">
         <f>ROUND(AVERAGE(F10:F11),2)</f>
-        <v/>
+        <v>17.44</v>
       </c>
       <c r="G12" s="22">
         <f>ROUND(AVERAGE(G10:G11),4)</f>
-        <v/>
+        <v>0.4027</v>
       </c>
       <c r="H12" s="23">
         <f>ROUND(AVERAGE(H10:H11),2)</f>
-        <v/>
+        <v>0.29</v>
       </c>
       <c r="I12" s="23">
         <f>ROUND(AVERAGE(I10:I11),2)</f>
-        <v/>
+        <v>95.66</v>
       </c>
     </row>
     <row r="13"/>
